--- a/Sufficient data WITH_PO/forecast_summary_B0BZQ1TNW8_WITH_PO.xlsx
+++ b/Sufficient data WITH_PO/forecast_summary_B0BZQ1TNW8_WITH_PO.xlsx
@@ -487,12 +487,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5.39</v>
+        <v>16.14</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -544,12 +544,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>W25</t>
+          <t>W27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4.39</v>
+        <v>15.01</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.88</v>
+        <v>1.05</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -601,12 +601,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>W26</t>
+          <t>W28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>114</v>
+        <v>241</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3.36</v>
+        <v>6.78</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.13</v>
+        <v>0.83</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -658,12 +658,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W27</t>
+          <t>W29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.34</v>
+        <v>11.81</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -715,12 +715,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W28</t>
+          <t>W30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>241</v>
+        <v>118</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.64</v>
+        <v>10.81</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>W29</t>
+          <t>W31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -818,7 +818,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -829,12 +829,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W30</t>
+          <t>W32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2025-07-20</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -875,7 +875,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -886,12 +886,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W31</t>
+          <t>W33</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -914,16 +914,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>7.73</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -943,12 +943,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>W32</t>
+          <t>W34</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -971,16 +971,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1000,12 +1000,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>W33</t>
+          <t>W35</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>6.02</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1046,7 +1046,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0.87</v>
+        <v>1.07</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1057,12 +1057,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>W34</t>
+          <t>W36</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1103,7 +1103,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0.99</v>
+        <v>0.92</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1114,12 +1114,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W35</t>
+          <t>W37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1142,16 +1142,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1160,7 +1160,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0.97</v>
+        <v>0.92</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1171,12 +1171,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W36</t>
+          <t>W38</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1185,7 +1185,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1199,16 +1199,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.08</v>
+        <v>0.88</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W37</t>
+          <t>W39</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1242,7 +1242,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1256,16 +1256,16 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0.84</v>
+        <v>1.16</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1285,12 +1285,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W38</t>
+          <t>W40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1313,16 +1313,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Urgent</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0.91</v>
+        <v>1.13</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -1342,12 +1342,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>W39</t>
+          <t>W41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1356,7 +1356,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-01-22 to 2025-06-01</t>
+          <t>2023-01-22 to 2025-06-15</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6215 units</t>
+          <t>6431 units</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1979</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1068</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>593</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>109</t>
         </is>
       </c>
     </row>
